--- a/results/Int Task Remove ACC 0.6/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC 0.6/Rando_10_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5344320486815416</v>
+        <v>0.5680454940596928</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5312807881773399</v>
+        <v>0.5680454940596928</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5299168883854483</v>
+        <v>0.5564908722109534</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5351689892257844</v>
+        <v>0.5564908722109534</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5551269724190617</v>
+        <v>0.5722471747319617</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5551269724190617</v>
+        <v>0.5690959142277601</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5344320486815416</v>
+        <v>0.5375833091857433</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5344320486815416</v>
+        <v>0.5375833091857433</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.534745528305366</v>
+        <v>0.5401846632069756</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5547035114986434</v>
+        <v>0.5401846632069756</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5449362503622138</v>
+        <v>0.5342120860883539</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5449362503622138</v>
+        <v>0.5429895155554385</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5417849898580122</v>
+        <v>0.5458272964358157</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5438858301941466</v>
+        <v>0.5464542556834646</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.588113458549564</v>
+        <v>0.5485550960195991</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.588113458549564</v>
+        <v>0.5485550960195991</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5933655593899001</v>
+        <v>0.5448868575643424</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5933655593899001</v>
+        <v>0.5393212771001817</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5793966175812018</v>
+        <v>0.5333322357156028</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.580447037749269</v>
+        <v>0.5343826558836701</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5444192724111588</v>
+        <v>0.5342891388530334</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5444192724111588</v>
+        <v>0.5342891388530334</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5376932904823372</v>
+        <v>0.5250223914017017</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5412680119069572</v>
+        <v>0.5004392666157371</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5424284133716182</v>
+        <v>0.5135448223176418</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5424284133716182</v>
+        <v>0.5229986038302469</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5340250520270804</v>
+        <v>0.5597633097125998</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5725771186217433</v>
+        <v>0.5818221332420115</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5868595400542662</v>
+        <v>0.5808981586364954</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5826578593819973</v>
+        <v>0.5804746977160771</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5826578593819973</v>
+        <v>0.6392982271278418</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.584021759173889</v>
+        <v>0.63614696662364</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5732040778693923</v>
+        <v>0.6223650588762151</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5753049182055268</v>
+        <v>0.6054812834224599</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5754148995021207</v>
+        <v>0.6148415479044282</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5751014198782962</v>
+        <v>0.600135665551487</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5684083664813888</v>
+        <v>0.600135665551487</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5673579463133216</v>
+        <v>0.600135665551487</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.564333131371671</v>
+        <v>0.4971944890808988</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5753595795685045</v>
+        <v>0.4865309133057612</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5499130686757462</v>
+        <v>0.4791779721292906</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5689964700613788</v>
+        <v>0.4869379099602223</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5472070019230262</v>
+        <v>0.4683273622928795</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.556000895656068</v>
+        <v>0.4648955506967677</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5576124180079555</v>
+        <v>0.4645820710729432</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5491925923974605</v>
+        <v>0.4813887937620189</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6293050762624799</v>
+        <v>0.4866902874002265</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6369879613287321</v>
+        <v>0.4866902874002265</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6207917336213482</v>
+        <v>0.4799313769394905</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6258238718684966</v>
+        <v>0.5076440293985933</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6320658043781776</v>
+        <v>0.5445187165775401</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6685664234345776</v>
+        <v>0.5380456257738205</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6817213719343537</v>
+        <v>0.5403499644371855</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6669713653486473</v>
+        <v>0.5681172782592661</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6669713653486473</v>
+        <v>0.5983101077421564</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6677083058928901</v>
+        <v>0.5983101077421564</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6741043439319301</v>
+        <v>0.622112167751113</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6675818603303391</v>
+        <v>0.5746674218276653</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6686322804984063</v>
+        <v>0.5767353336318853</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7007606490872211</v>
+        <v>0.5941690155686099</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6985662917204499</v>
+        <v>0.5938555359447855</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6696003793366876</v>
+        <v>0.6036227970812149</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6579357761913542</v>
+        <v>0.6244441663812861</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6507257448433919</v>
+        <v>0.6210729432838966</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6550374068122546</v>
+        <v>0.5770316904191144</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5202984642132715</v>
+        <v>0.547916282500461</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.529059429414399</v>
+        <v>0.5255545164774373</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5294828903348173</v>
+        <v>0.5560825584152156</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4832861357709228</v>
+        <v>0.5577599378309317</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4832861357709228</v>
+        <v>0.5753477252970154</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4843365559389901</v>
+        <v>0.558222254419009</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4884776481125366</v>
+        <v>0.4654810199942046</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4830991017096494</v>
+        <v>0.4436750875898949</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4567174205105239</v>
+        <v>0.430899475777772</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4879060087985038</v>
+        <v>0.4188166802771265</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4929987355443745</v>
+        <v>0.4119530570849029</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4785786728484497</v>
+        <v>0.4212968573009141</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.443424830747346</v>
+        <v>0.4446754563894523</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4825821237585943</v>
+        <v>0.4798734227233213</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4682997023260715</v>
+        <v>0.4744066278549037</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4705045968230552</v>
+        <v>0.5021904059429414</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5285582571586629</v>
+        <v>0.5519612233608178</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5473723031532363</v>
+        <v>0.5489587998208687</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5275631569242116</v>
+        <v>0.5333783356602829</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5084079713390058</v>
+        <v>0.5276915781986776</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4952754142409315</v>
+        <v>0.508024683227523</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.492267063565238</v>
+        <v>0.5019697847791155</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4969745264877111</v>
+        <v>0.5062926424488291</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4978326440293986</v>
+        <v>0.5107808013487527</v>
       </c>
     </row>
   </sheetData>
